--- a/sources/yoshimitsu_step10.xlsx
+++ b/sources/yoshimitsu_step10.xlsx
@@ -7897,12 +7897,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>ms[!]</t>
+          <t>ms!</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>[!]h</t>
+          <t>!h</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>[!]m</t>
+          <t>!m</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -10740,12 +10740,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>[!]-[!]</t>
+          <t>!-!</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
@@ -12364,12 +12364,12 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">

--- a/sources/yoshimitsu_step10.xlsx
+++ b/sources/yoshimitsu_step10.xlsx
@@ -883,6 +883,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -950,6 +955,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -1015,6 +1025,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -12320,6 +12335,11 @@
           <t>hmmhhLm!!!</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="AB134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -12372,6 +12392,11 @@
           <t>hmmhmmmm!!</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="AB135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -12424,6 +12449,11 @@
           <t>hhmhhLm!!!</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="AB136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -12476,6 +12506,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="AB137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -12528,6 +12563,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="AB138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -12580,6 +12620,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="AB139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -12630,6 +12675,11 @@
       <c r="U140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
